--- a/research/traditional_assets/database/data/germany/germany_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3295</v>
+        <v>0.2245</v>
       </c>
       <c r="E2">
-        <v>0.626</v>
+        <v>0.1654</v>
       </c>
       <c r="F2">
-        <v>-0.2909</v>
+        <v>-0.792</v>
       </c>
       <c r="G2">
-        <v>0.007562546462590233</v>
+        <v>0.01314553476309282</v>
       </c>
       <c r="H2">
-        <v>0.004446513308275378</v>
+        <v>0.01226916577888663</v>
       </c>
       <c r="I2">
-        <v>0.009538830837211543</v>
+        <v>0.00397105422800766</v>
       </c>
       <c r="J2">
-        <v>0.007146054976298864</v>
+        <v>0.002671702668539333</v>
       </c>
       <c r="K2">
-        <v>510.763</v>
+        <v>229.845</v>
       </c>
       <c r="L2">
-        <v>0.1774308185058326</v>
+        <v>0.1258931432342945</v>
       </c>
       <c r="M2">
-        <v>136.8413</v>
+        <v>294.0054</v>
       </c>
       <c r="N2">
-        <v>0.01503210384839733</v>
+        <v>0.05856634608489176</v>
       </c>
       <c r="O2">
-        <v>0.2679154519806642</v>
+        <v>1.279146381256934</v>
       </c>
       <c r="P2">
-        <v>136.8413</v>
+        <v>294.0054</v>
       </c>
       <c r="Q2">
-        <v>0.01503210384839733</v>
+        <v>0.05856634608489176</v>
       </c>
       <c r="R2">
-        <v>0.2679154519806642</v>
+        <v>1.279146381256934</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3817.565</v>
+        <v>726.164</v>
       </c>
       <c r="V2">
-        <v>0.4193619435653342</v>
+        <v>0.1446530306531422</v>
       </c>
       <c r="W2">
-        <v>0.5961338086098162</v>
+        <v>0.02315152844814977</v>
       </c>
       <c r="X2">
-        <v>0.03384377212651868</v>
+        <v>0.06591110772994889</v>
       </c>
       <c r="Y2">
-        <v>0.5622900364832976</v>
+        <v>-0.04275957928179912</v>
       </c>
       <c r="Z2">
-        <v>-5.948944375476968</v>
+        <v>2.313012094292559</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.321411876257187e-05</v>
       </c>
       <c r="AB2">
-        <v>0.03320457757631572</v>
+        <v>0.06570689281610761</v>
       </c>
       <c r="AC2">
-        <v>-0.03307795275493824</v>
+        <v>-0.06555270361180884</v>
       </c>
       <c r="AD2">
-        <v>1010.349</v>
+        <v>693.5690000000001</v>
       </c>
       <c r="AE2">
-        <v>15.1147461107631</v>
+        <v>13.11993365056498</v>
       </c>
       <c r="AF2">
-        <v>1025.463746110763</v>
+        <v>706.688933650565</v>
       </c>
       <c r="AG2">
-        <v>-2792.101253889237</v>
+        <v>-19.475066349435</v>
       </c>
       <c r="AH2">
-        <v>0.1012430350935546</v>
+        <v>0.1234018480424354</v>
       </c>
       <c r="AI2">
-        <v>0.3745091916651204</v>
+        <v>0.4145924271363332</v>
       </c>
       <c r="AJ2">
-        <v>-0.4424063697567681</v>
+        <v>-0.003894573234792015</v>
       </c>
       <c r="AK2">
-        <v>2.586689034257324</v>
+        <v>-0.01990552464050626</v>
       </c>
       <c r="AL2">
-        <v>0.038</v>
+        <v>0.227</v>
       </c>
       <c r="AM2">
-        <v>-0.346</v>
+        <v>0.141</v>
       </c>
       <c r="AN2">
-        <v>33.14575815235221</v>
+        <v>69.74748592115849</v>
       </c>
       <c r="AO2">
-        <v>634.2105263157895</v>
+        <v>15.37444933920705</v>
       </c>
       <c r="AP2">
-        <v>-91.5983614555881</v>
+        <v>-1.958474089846641</v>
       </c>
       <c r="AQ2">
-        <v>-69.65317919075144</v>
+        <v>24.7517730496454</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bitcoin Group SE (XTRA:ADE)</t>
+          <t>mwb fairtrade Wertpapierhandelsbank AG (XTRA:MWB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,118 +725,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.769</v>
+        <v>0.257</v>
       </c>
       <c r="E3">
-        <v>1.35</v>
+        <v>0.059</v>
       </c>
       <c r="G3">
-        <v>0.4076433121019108</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.4076433121019108</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.767515923566879</v>
+        <v>0.05690968498531018</v>
       </c>
       <c r="J3">
-        <v>0.5522090221617882</v>
+        <v>0.03649880758192489</v>
       </c>
       <c r="K3">
-        <v>19.2</v>
+        <v>6.63</v>
       </c>
       <c r="L3">
-        <v>0.6114649681528662</v>
+        <v>0.1078048780487805</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>10.8916</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1861811965811966</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.642775263951735</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>10.8916</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1861811965811966</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.642775263951735</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>20.9</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0.09071180555555555</v>
+        <v>1.70940170940171e-05</v>
       </c>
       <c r="W3">
-        <v>0.4571428571428571</v>
+        <v>0.1453947368421052</v>
       </c>
       <c r="X3">
-        <v>0.03329804365818328</v>
+        <v>0.07338139156130093</v>
       </c>
       <c r="Y3">
-        <v>0.4238448134846738</v>
+        <v>0.07201334528080432</v>
       </c>
       <c r="Z3">
-        <v>1.08865235932462</v>
+        <v>0.9731124771406749</v>
       </c>
       <c r="AA3">
-        <v>0.601163654816772</v>
+        <v>0.03551744505872777</v>
       </c>
       <c r="AB3">
-        <v>0.03326168774325378</v>
+        <v>0.06338481269483298</v>
       </c>
       <c r="AC3">
-        <v>0.5679019670735183</v>
+        <v>-0.02786736763610521</v>
       </c>
       <c r="AD3">
-        <v>0.612</v>
+        <v>16.4</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>7.100271867017121</v>
       </c>
       <c r="AF3">
-        <v>0.612</v>
+        <v>23.50027186701712</v>
       </c>
       <c r="AG3">
-        <v>-20.288</v>
+        <v>23.49927186701712</v>
       </c>
       <c r="AH3">
-        <v>0.002649213027894655</v>
+        <v>0.2865877311373843</v>
       </c>
       <c r="AI3">
-        <v>0.004460251289974638</v>
+        <v>0.4174095628263652</v>
       </c>
       <c r="AJ3">
-        <v>-0.09655802619555286</v>
+        <v>0.2865790309105088</v>
       </c>
       <c r="AK3">
-        <v>-0.1744274021597084</v>
+        <v>0.4173992147273959</v>
       </c>
       <c r="AL3">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.02539419087136929</v>
-      </c>
-      <c r="AO3">
-        <v>634.2105263157895</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="AP3">
-        <v>-0.8418257261410788</v>
-      </c>
-      <c r="AQ3">
-        <v>803.3333333333334</v>
+        <v>4.776274769718927</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mwb fairtrade Wertpapierhandelsbank AG (XTRA:MWB)</t>
+          <t>Bitcoin Group SE (XTRA:ADE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +853,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.386</v>
+        <v>0.444</v>
       </c>
       <c r="E4">
-        <v>1.742</v>
+        <v>0.0788</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1.611510791366906</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1.611510791366906</v>
       </c>
       <c r="I4">
-        <v>0.04638737534937275</v>
+        <v>0.2510791366906475</v>
       </c>
       <c r="J4">
-        <v>0.03024582244063831</v>
+        <v>0.1255395683453237</v>
       </c>
       <c r="K4">
-        <v>19.3</v>
+        <v>1.03</v>
       </c>
       <c r="L4">
-        <v>0.3010920436817473</v>
+        <v>0.07410071942446043</v>
       </c>
       <c r="M4">
-        <v>15.8685</v>
+        <v>0.523</v>
       </c>
       <c r="N4">
-        <v>0.1469305555555555</v>
+        <v>0.005522703273495248</v>
       </c>
       <c r="O4">
-        <v>0.82220207253886</v>
+        <v>0.5077669902912622</v>
       </c>
       <c r="P4">
-        <v>15.8685</v>
+        <v>0.523</v>
       </c>
       <c r="Q4">
-        <v>0.1469305555555555</v>
+        <v>0.005522703273495248</v>
       </c>
       <c r="R4">
-        <v>0.82220207253886</v>
+        <v>0.5077669902912622</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,67 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.001</v>
+        <v>20.2</v>
       </c>
       <c r="V4">
-        <v>9.259259259259259e-06</v>
+        <v>0.2133051742344245</v>
       </c>
       <c r="W4">
-        <v>0.7451737451737452</v>
+        <v>0.007540263543191802</v>
       </c>
       <c r="X4">
-        <v>0.03501644743448146</v>
+        <v>0.06588897361143775</v>
       </c>
       <c r="Y4">
-        <v>0.7101572977392638</v>
+        <v>-0.05834871006824595</v>
       </c>
       <c r="Z4">
-        <v>2.106622978753318</v>
+        <v>0.1244270982526497</v>
       </c>
       <c r="AA4">
-        <v>0.06371654456474143</v>
+        <v>0.01562052420509883</v>
       </c>
       <c r="AB4">
-        <v>0.03314624065027345</v>
+        <v>0.06574827239495272</v>
       </c>
       <c r="AC4">
-        <v>0.03057030391446798</v>
+        <v>-0.05012774818985389</v>
       </c>
       <c r="AD4">
-        <v>10.5</v>
+        <v>0.489</v>
       </c>
       <c r="AE4">
-        <v>4.382846200526037</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>14.88284620052604</v>
+        <v>0.489</v>
       </c>
       <c r="AG4">
-        <v>14.88184620052604</v>
+        <v>-19.711</v>
       </c>
       <c r="AH4">
-        <v>0.1211141071410366</v>
+        <v>0.005137148199897046</v>
       </c>
       <c r="AI4">
-        <v>0.2460672262542532</v>
+        <v>0.005780893496790363</v>
       </c>
       <c r="AJ4">
-        <v>0.1211069548567893</v>
+        <v>-0.2628518849431249</v>
       </c>
       <c r="AK4">
-        <v>0.246054760815099</v>
+        <v>-0.3061237167839227</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.008000000000000007</v>
       </c>
       <c r="AN4">
-        <v>2.727272727272727</v>
+        <v>0.1373595505617977</v>
+      </c>
+      <c r="AO4">
+        <v>47.16216216216217</v>
       </c>
       <c r="AP4">
-        <v>3.86541459753923</v>
+        <v>-5.536797752808988</v>
+      </c>
+      <c r="AQ4">
+        <v>-436.2499999999997</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Varengold Bank AG (XTRA:VG8)</t>
+          <t>Lang &amp; Schwarz Aktiengesellschaft (XTRA:LUS1)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,7 +987,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.044</v>
+        <v>0.322</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -999,87 +1002,96 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>9.1</v>
+        <v>-18.7</v>
       </c>
       <c r="L5">
-        <v>0.2369791666666667</v>
+        <v>-0.0210727969348659</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>14.8208</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1688018223234624</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>-0.7925561497326203</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>14.8208</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1688018223234624</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>-0.7925561497326203</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>742.1</v>
+        <v>684.4</v>
       </c>
       <c r="V5">
-        <v>14.75347912524851</v>
+        <v>7.79498861047836</v>
       </c>
       <c r="W5">
-        <v>0.2126168224299065</v>
+        <v>-0.1833333333333333</v>
       </c>
       <c r="X5">
-        <v>0.07512514654559159</v>
+        <v>0.1879567517278754</v>
       </c>
       <c r="Y5">
-        <v>0.1374916758843149</v>
+        <v>-0.3712900850612088</v>
       </c>
       <c r="Z5">
-        <v>0.9275362318840578</v>
+        <v>26.89090909090909</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03251678698391471</v>
+        <v>0.05851876857621274</v>
       </c>
       <c r="AC5">
-        <v>-0.03251678698391471</v>
+        <v>-0.05851876857621274</v>
       </c>
       <c r="AD5">
-        <v>165.6</v>
+        <v>567.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>165.6</v>
+        <v>567.7</v>
       </c>
       <c r="AG5">
-        <v>-576.5</v>
+        <v>-116.6999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.7670217693376564</v>
+        <v>0.8660564454614799</v>
       </c>
       <c r="AI5">
-        <v>0.7534121929026387</v>
+        <v>0.907158836689038</v>
       </c>
       <c r="AJ5">
-        <v>1.095591030026606</v>
+        <v>4.038062283737031</v>
       </c>
       <c r="AK5">
-        <v>1.103771778671262</v>
+        <v>1.99146757679181</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AM5">
+        <v>0.153</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
         <v>0</v>
       </c>
     </row>
@@ -1091,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lang &amp; Schwarz Aktiengesellschaft (XTRA:LUS)</t>
+          <t>JDC Group AG (XTRA:JDC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,109 +1112,109 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.29</v>
-      </c>
-      <c r="E6">
-        <v>0.496</v>
+        <v>0.141</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.01023672424824056</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.001249602023087209</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.0009724793975590254</v>
       </c>
       <c r="K6">
-        <v>52.4</v>
+        <v>1.15</v>
       </c>
       <c r="L6">
-        <v>0.05171222737590053</v>
+        <v>0.007357645553422903</v>
       </c>
       <c r="M6">
-        <v>14.931</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.05118615015426809</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.2849427480916031</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>14.931</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.05118615015426809</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.2849427480916031</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>505</v>
+        <v>17.4</v>
       </c>
       <c r="V6">
-        <v>1.731230716489544</v>
+        <v>0.0748709122203098</v>
       </c>
       <c r="W6">
-        <v>1.112526539278132</v>
+        <v>0.03616352201257862</v>
       </c>
       <c r="X6">
-        <v>0.05226918905185816</v>
+        <v>0.06737906194646059</v>
       </c>
       <c r="Y6">
-        <v>1.060257350226274</v>
+        <v>-0.03121553993388198</v>
       </c>
       <c r="Z6">
-        <v>84.44166666666666</v>
+        <v>3.187945867568874</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.003100211676744163</v>
       </c>
       <c r="AB6">
-        <v>0.03268038429887719</v>
+        <v>0.06514047815488526</v>
       </c>
       <c r="AC6">
-        <v>-0.03268038429887719</v>
+        <v>-0.06204026647814109</v>
       </c>
       <c r="AD6">
-        <v>436</v>
+        <v>19.3</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.228436018957346</v>
       </c>
       <c r="AF6">
-        <v>436</v>
+        <v>19.52843601895735</v>
       </c>
       <c r="AG6">
-        <v>-69</v>
+        <v>2.128436018957348</v>
       </c>
       <c r="AH6">
-        <v>0.599148000549677</v>
+        <v>0.07751580697896228</v>
       </c>
       <c r="AI6">
-        <v>0.8104089219330854</v>
+        <v>0.3436384561497148</v>
       </c>
       <c r="AJ6">
-        <v>-0.309833857207005</v>
+        <v>0.009075385719049023</v>
       </c>
       <c r="AK6">
-        <v>-2.090909090909091</v>
+        <v>0.05398225833593776</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.368</v>
+        <v>-0.004</v>
+      </c>
+      <c r="AN6">
+        <v>80.08298755186722</v>
+      </c>
+      <c r="AP6">
+        <v>8.8316847259641</v>
       </c>
       <c r="AQ6">
         <v>-0</v>
@@ -1216,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>flatexDEGIRO AG (XTRA:FTK)</t>
+          <t>EUWAX Aktiengesellschaft (DB:EUX)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,106 +1237,115 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.369</v>
-      </c>
-      <c r="F7">
-        <v>-0.09179999999999999</v>
+        <v>0.198</v>
+      </c>
+      <c r="E7">
+        <v>-0.294</v>
       </c>
       <c r="G7">
-        <v>0.01595838866755201</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.001204230577755963</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.0006021152888779814</v>
       </c>
       <c r="K7">
-        <v>65.90000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="L7">
-        <v>0.1458610004426737</v>
+        <v>0.02037383177570094</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>6.16</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.02035018169805088</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>5.651376146788991</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>6.16</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.02035018169805088</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>5.651376146788991</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>1610.5</v>
+        <v>3.66</v>
       </c>
       <c r="V7">
-        <v>0.6405870888190606</v>
+        <v>0.01209117938553023</v>
       </c>
       <c r="W7">
-        <v>0.2872711421098518</v>
+        <v>0.01013953488372093</v>
       </c>
       <c r="X7">
-        <v>0.03452054534385984</v>
+        <v>0.06588272080438333</v>
       </c>
       <c r="Y7">
-        <v>0.252750596765992</v>
+        <v>-0.0557431859206624</v>
       </c>
       <c r="Z7">
-        <v>-0.5805705474171164</v>
+        <v>0.5121584093508398</v>
       </c>
       <c r="AA7">
-        <v>-0</v>
+        <v>0.0003083784085975683</v>
       </c>
       <c r="AB7">
-        <v>0.03288598194554189</v>
+        <v>0.06572510072634939</v>
       </c>
       <c r="AC7">
-        <v>-0.03288598194554189</v>
+        <v>-0.06541672231775182</v>
       </c>
       <c r="AD7">
-        <v>248.4</v>
+        <v>0.66</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>0.80286832045028</v>
       </c>
       <c r="AF7">
-        <v>248.4</v>
+        <v>1.46286832045028</v>
       </c>
       <c r="AG7">
-        <v>-1362.1</v>
+        <v>-2.19713167954972</v>
       </c>
       <c r="AH7">
-        <v>0.0899185520361991</v>
+        <v>0.004809490154166607</v>
       </c>
       <c r="AI7">
-        <v>0.306288532675709</v>
+        <v>0.0160291731716532</v>
       </c>
       <c r="AJ7">
-        <v>-1.182378472222222</v>
+        <v>-0.007311516498427372</v>
       </c>
       <c r="AK7">
-        <v>1.703689806128831</v>
+        <v>-0.02508059064359214</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>2.933333333333334</v>
+      </c>
+      <c r="AP7">
+        <v>-9.765029686887646</v>
       </c>
     </row>
     <row r="8">
@@ -1335,7 +1356,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JDC Group AG (XTRA:A8A)</t>
+          <t>Berliner Effektengesellschaft AG (DB:BFV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,112 +1365,109 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.133</v>
+        <v>0.251</v>
+      </c>
+      <c r="E8">
+        <v>0.252</v>
       </c>
       <c r="G8">
-        <v>0.01092489137181875</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0001269450872467162</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>6.347254362335811e-05</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>-0.126</v>
+        <v>36.6</v>
       </c>
       <c r="L8">
-        <v>-0.000782122905027933</v>
+        <v>0.1868300153139357</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>14.07</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.01248447204968944</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.3844262295081967</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>14.07</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.01248447204968944</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.3844262295081967</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>11</v>
+        <v>0.249</v>
       </c>
       <c r="V8">
-        <v>0.03128555176336746</v>
+        <v>0.0002209405501330967</v>
       </c>
       <c r="W8">
-        <v>-0.003888888888888889</v>
+        <v>0.2304785894206549</v>
       </c>
       <c r="X8">
-        <v>0.03427838549098074</v>
+        <v>0.06593324184846003</v>
       </c>
       <c r="Y8">
-        <v>-0.03816727437986963</v>
+        <v>0.1645453475721949</v>
       </c>
       <c r="Z8">
-        <v>3.284889489663132</v>
+        <v>1.127397662333178</v>
       </c>
       <c r="AA8">
-        <v>0.0002085002914305537</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03319228500824512</v>
+        <v>0.06568868490586585</v>
       </c>
       <c r="AC8">
-        <v>-0.03298378471681457</v>
+        <v>-0.06568868490586585</v>
       </c>
       <c r="AD8">
-        <v>28</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AE8">
-        <v>0.0427457322227701</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>28.04274573222277</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AG8">
-        <v>17.04274573222277</v>
+        <v>8.211</v>
       </c>
       <c r="AH8">
-        <v>0.07386614401952102</v>
+        <v>0.007450724816373981</v>
       </c>
       <c r="AI8">
-        <v>0.4686072704234717</v>
+        <v>0.0369496855345912</v>
       </c>
       <c r="AJ8">
-        <v>0.04623106226699601</v>
+        <v>0.007233016593391008</v>
       </c>
       <c r="AK8">
-        <v>0.3489309512953783</v>
+        <v>0.03590120282802314</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.008</v>
-      </c>
-      <c r="AN8">
-        <v>965.5172413793103</v>
-      </c>
-      <c r="AP8">
-        <v>587.6808873180265</v>
-      </c>
-      <c r="AQ8">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1469,10 +1487,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.412</v>
+        <v>0.27</v>
       </c>
       <c r="E9">
-        <v>0.622</v>
+        <v>0.356</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1481,34 +1499,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>5.143685924559666e-05</v>
+        <v>8.053401812449186e-05</v>
       </c>
       <c r="J9">
-        <v>3.401016376348194e-05</v>
+        <v>5.152320467906971e-05</v>
       </c>
       <c r="K9">
-        <v>145.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L9">
-        <v>0.4633056796426292</v>
+        <v>0.348326359832636</v>
       </c>
       <c r="M9">
-        <v>51.97199999999999</v>
+        <v>101.992</v>
       </c>
       <c r="N9">
-        <v>0.01587658469528028</v>
+        <v>0.03591773489223834</v>
       </c>
       <c r="O9">
-        <v>0.3579338842975207</v>
+        <v>1.531411411411411</v>
       </c>
       <c r="P9">
-        <v>51.97199999999999</v>
+        <v>101.992</v>
       </c>
       <c r="Q9">
-        <v>0.01587658469528028</v>
+        <v>0.03591773489223834</v>
       </c>
       <c r="R9">
-        <v>0.3579338842975207</v>
+        <v>1.531411411411411</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1517,55 +1535,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.236</v>
+        <v>0.248</v>
       </c>
       <c r="V9">
-        <v>7.20940888956774e-05</v>
+        <v>8.733624454148472e-05</v>
       </c>
       <c r="W9">
-        <v>1.457831325301205</v>
+        <v>0.3377281947261663</v>
       </c>
       <c r="X9">
-        <v>0.03332338493569005</v>
+        <v>0.06584782175686035</v>
       </c>
       <c r="Y9">
-        <v>1.424507940365515</v>
+        <v>0.271880372969306</v>
       </c>
       <c r="Z9">
-        <v>2.867038611417487</v>
+        <v>0.9011131550208928</v>
       </c>
       <c r="AA9">
-        <v>9.75084526905346e-05</v>
+        <v>4.642823752514374e-05</v>
       </c>
       <c r="AB9">
-        <v>0.03326962924575246</v>
+        <v>0.06576641419312645</v>
       </c>
       <c r="AC9">
-        <v>-0.03317212079306193</v>
+        <v>-0.06571998595560131</v>
       </c>
       <c r="AD9">
-        <v>15.2</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AE9">
-        <v>0.01939844156215004</v>
+        <v>0.01800947867298578</v>
       </c>
       <c r="AF9">
-        <v>15.21939844156215</v>
+        <v>8.478009478672986</v>
       </c>
       <c r="AG9">
-        <v>14.98339844156215</v>
+        <v>8.230009478672986</v>
       </c>
       <c r="AH9">
-        <v>0.004627758284508622</v>
+        <v>0.002976747634881267</v>
       </c>
       <c r="AI9">
-        <v>0.07164787469139311</v>
+        <v>0.05733110358031758</v>
       </c>
       <c r="AJ9">
-        <v>0.004556324793569855</v>
+        <v>0.002889923012005756</v>
       </c>
       <c r="AK9">
-        <v>0.07061531934925981</v>
+        <v>0.05574753742640594</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1574,10 +1592,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>760</v>
+        <v>445.2631578947369</v>
       </c>
       <c r="AP9">
-        <v>749.1699220781073</v>
+        <v>433.1583936143677</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1606,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EUWAX Aktiengesellschaft (DB:EUX)</t>
+          <t>Sino AG (DB:XTP)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1597,10 +1615,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.257</v>
+        <v>0.138</v>
       </c>
       <c r="E10">
-        <v>0.105</v>
+        <v>1.914</v>
+      </c>
+      <c r="F10">
+        <v>-0.792</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1609,34 +1630,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>8.836891521720724e-05</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>5.553963427900123e-05</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>12.1</v>
+        <v>136.9</v>
       </c>
       <c r="L10">
-        <v>0.1425206124852768</v>
+        <v>13.03809523809524</v>
       </c>
       <c r="M10">
-        <v>16.6</v>
+        <v>145.548</v>
       </c>
       <c r="N10">
-        <v>0.04346687614558786</v>
+        <v>2.267102803738318</v>
       </c>
       <c r="O10">
-        <v>1.371900826446281</v>
+        <v>1.063170197224251</v>
       </c>
       <c r="P10">
-        <v>16.6</v>
+        <v>145.548</v>
       </c>
       <c r="Q10">
-        <v>0.04346687614558786</v>
+        <v>2.267102803738318</v>
       </c>
       <c r="R10">
-        <v>1.371900826446281</v>
+        <v>1.063170197224251</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1645,67 +1666,61 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>4.18</v>
+        <v>0.004</v>
       </c>
       <c r="V10">
-        <v>0.0109452736318408</v>
+        <v>6.230529595015576e-05</v>
       </c>
       <c r="W10">
-        <v>0.1138287864534337</v>
+        <v>3.474619289340102</v>
       </c>
       <c r="X10">
-        <v>0.03329305173568518</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y10">
-        <v>0.0805357347177485</v>
+        <v>3.408827878136846</v>
       </c>
       <c r="Z10">
-        <v>0.8203811084371853</v>
+        <v>0.2665583508923358</v>
       </c>
       <c r="AA10">
-        <v>4.556366673200292e-05</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03325476780404065</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC10">
-        <v>-0.03320920413730865</v>
+        <v>-0.06579141120325535</v>
       </c>
       <c r="AD10">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>0.5274873954902956</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.8644873954902956</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>-3.315512604509704</v>
+        <v>-0.004</v>
       </c>
       <c r="AH10">
-        <v>0.002258536055350053</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.007977589487737217</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>-0.008757655727837935</v>
+        <v>-6.230917814194032e-05</v>
       </c>
       <c r="AK10">
-        <v>-0.03182347667483191</v>
+        <v>-2.401018031645418e-05</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>2.982300884955752</v>
-      </c>
-      <c r="AP10">
-        <v>-29.34081950893543</v>
       </c>
     </row>
     <row r="11">
@@ -1716,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Berliner Effektengesellschaft AG (DB:BFV)</t>
+          <t>Valora Effekten Handel AG (DB:VEH)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1725,10 +1740,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.408</v>
-      </c>
-      <c r="E11">
-        <v>0.63</v>
+        <v>-0.118</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1743,85 +1755,82 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>80.09999999999999</v>
+        <v>-0.235</v>
       </c>
       <c r="L11">
-        <v>0.2464615384615385</v>
+        <v>-0.5662650602409639</v>
       </c>
       <c r="M11">
-        <v>15.946</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.011954419371767</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.1990761548064919</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>15.946</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.011954419371767</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.1990761548064919</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>0.237</v>
+        <v>0.002</v>
       </c>
       <c r="V11">
-        <v>0.0001776744883424544</v>
+        <v>0.0007874015748031496</v>
       </c>
       <c r="W11">
-        <v>0.8919821826280623</v>
+        <v>-0.09073359073359073</v>
       </c>
       <c r="X11">
-        <v>0.03340915876205661</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y11">
-        <v>0.8585730238660056</v>
+        <v>-0.1565250019368461</v>
       </c>
       <c r="Z11">
-        <v>3.266594299039119</v>
+        <v>0.160355486862442</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03321687014438632</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC11">
-        <v>-0.03321687014438632</v>
+        <v>-0.06579141120325535</v>
       </c>
       <c r="AD11">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>14.963</v>
+        <v>-0.002</v>
       </c>
       <c r="AH11">
-        <v>0.01126677043955229</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.05801526717557252</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>0.01109304651398993</v>
+        <v>-0.0007880220646178092</v>
       </c>
       <c r="AK11">
-        <v>0.0571623949908887</v>
+        <v>-0.0009765625</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1838,7 +1847,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sino AG (DB:XTP)</t>
+          <t>Baader Bank Aktiengesellschaft (XTRA:BWB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1847,13 +1856,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.4429999999999999</v>
-      </c>
-      <c r="E12">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="F12">
-        <v>-0.49</v>
+        <v>0.142</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1862,91 +1865,79 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>-5.90732775125433e-05</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>-2.953663875627165e-05</v>
       </c>
       <c r="K12">
-        <v>30.8</v>
+        <v>-1.22</v>
       </c>
       <c r="L12">
-        <v>0.7162790697674418</v>
+        <v>-0.004782438259506076</v>
       </c>
       <c r="M12">
-        <v>8.026199999999999</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.03485106382978723</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.260590909090909</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>8.026199999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.03485106382978723</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.260590909090909</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>3.907946157186279e-05</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>2.961538461538462</v>
+        <v>-0.006545064377682403</v>
       </c>
       <c r="X12">
-        <v>0.03326426946963817</v>
+        <v>0.07270578070686279</v>
       </c>
       <c r="Y12">
-        <v>2.928274192068824</v>
-      </c>
-      <c r="Z12">
-        <v>4.142581888246628</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
+        <v>-0.07925084508454519</v>
       </c>
       <c r="AB12">
-        <v>0.03326426946963817</v>
-      </c>
-      <c r="AC12">
-        <v>-0.03326426946963817</v>
+        <v>0.06354164043257618</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>4.970347965467249</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>77.07034796546725</v>
       </c>
       <c r="AG12">
-        <v>-0.008999999999999999</v>
+        <v>77.07034796546725</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.2679120337238198</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.3155124991935688</v>
       </c>
       <c r="AJ12">
-        <v>-3.908098883586418e-05</v>
+        <v>0.2679120337238198</v>
       </c>
       <c r="AK12">
-        <v>-0.000228478586479145</v>
+        <v>0.3155124991935688</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1954,249 +1945,11 @@
       <c r="AM12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Valora Effekten Handel AG (DB:VEH)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.00063</v>
-      </c>
-      <c r="E13">
-        <v>-0.094</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0.189</v>
-      </c>
-      <c r="L13">
-        <v>0.1629310344827586</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>-0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>-0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0.002</v>
-      </c>
-      <c r="V13">
-        <v>0.0007220216606498195</v>
-      </c>
-      <c r="W13">
-        <v>0.08289473684210527</v>
-      </c>
-      <c r="X13">
-        <v>0.03326426946963817</v>
-      </c>
-      <c r="Y13">
-        <v>0.0496304673724671</v>
-      </c>
-      <c r="Z13">
-        <v>0.5092186128182616</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.03326426946963817</v>
-      </c>
-      <c r="AC13">
-        <v>-0.03326426946963817</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>-0.002</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>-0.000722543352601156</v>
-      </c>
-      <c r="AK13">
-        <v>-0.0007727975270479134</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Baader Bank Aktiengesellschaft (XTRA:BWB)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>0.215</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0.0009727893244307318</v>
-      </c>
-      <c r="J14">
-        <v>0.0008339743483692673</v>
-      </c>
-      <c r="K14">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="L14">
-        <v>0.2181714611221874</v>
-      </c>
-      <c r="M14">
-        <v>13.4976</v>
-      </c>
-      <c r="N14">
-        <v>0.04031541218637993</v>
-      </c>
-      <c r="O14">
-        <v>0.1762088772845953</v>
-      </c>
-      <c r="P14">
-        <v>13.4976</v>
-      </c>
-      <c r="Q14">
-        <v>0.04031541218637993</v>
-      </c>
-      <c r="R14">
-        <v>0.1762088772845953</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>923.4</v>
-      </c>
-      <c r="V14">
-        <v>2.758064516129032</v>
-      </c>
-      <c r="W14">
-        <v>0.7351247600767754</v>
-      </c>
-      <c r="X14">
-        <v>0.03708644777766268</v>
-      </c>
-      <c r="Y14">
-        <v>0.6980383122991127</v>
-      </c>
-      <c r="Z14">
-        <v>-1.825245062789256</v>
-      </c>
-      <c r="AA14">
-        <v>-0.001522207561853892</v>
-      </c>
-      <c r="AB14">
-        <v>0.03303903069085455</v>
-      </c>
-      <c r="AC14">
-        <v>-0.03456123825270845</v>
-      </c>
-      <c r="AD14">
-        <v>90.5</v>
-      </c>
-      <c r="AE14">
-        <v>10.14226834096185</v>
-      </c>
-      <c r="AF14">
-        <v>100.6422683409618</v>
-      </c>
-      <c r="AG14">
-        <v>-822.7577316590381</v>
-      </c>
-      <c r="AH14">
-        <v>0.231126548013838</v>
-      </c>
-      <c r="AI14">
-        <v>0.3506182867166253</v>
-      </c>
-      <c r="AJ14">
-        <v>1.68612500279828</v>
-      </c>
-      <c r="AK14">
-        <v>1.29291700363888</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>38.18565400843882</v>
-      </c>
-      <c r="AP14">
-        <v>-347.1551610375688</v>
+      <c r="AN12">
+        <v>73.64657814096016</v>
+      </c>
+      <c r="AP12">
+        <v>78.72354235492058</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2245</v>
+        <v>0.1205</v>
       </c>
       <c r="E2">
-        <v>0.1654</v>
+        <v>-0.01685</v>
       </c>
       <c r="F2">
-        <v>-0.792</v>
+        <v>0.008</v>
       </c>
       <c r="G2">
-        <v>0.01314553476309282</v>
+        <v>-0.0029464807335721</v>
       </c>
       <c r="H2">
-        <v>0.01226916577888663</v>
+        <v>-0.005054738499834895</v>
       </c>
       <c r="I2">
-        <v>0.00397105422800766</v>
+        <v>0.001167799310325024</v>
       </c>
       <c r="J2">
-        <v>0.002671702668539333</v>
+        <v>0.0009647957080300246</v>
       </c>
       <c r="K2">
-        <v>229.845</v>
+        <v>48.361</v>
       </c>
       <c r="L2">
-        <v>0.1258931432342945</v>
+        <v>0.06142015291218979</v>
       </c>
       <c r="M2">
-        <v>294.0054</v>
+        <v>78.08035</v>
       </c>
       <c r="N2">
-        <v>0.05856634608489176</v>
+        <v>0.01561013814750395</v>
       </c>
       <c r="O2">
-        <v>1.279146381256934</v>
+        <v>1.614531337234548</v>
       </c>
       <c r="P2">
-        <v>294.0054</v>
+        <v>76.23035</v>
       </c>
       <c r="Q2">
-        <v>0.05856634608489176</v>
+        <v>0.01524027869409625</v>
       </c>
       <c r="R2">
-        <v>1.279146381256934</v>
+        <v>1.576277372262774</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.02369354133274249</v>
       </c>
       <c r="U2">
-        <v>726.164</v>
+        <v>77.489</v>
       </c>
       <c r="V2">
-        <v>0.1446530306531422</v>
+        <v>0.01549191307303225</v>
       </c>
       <c r="W2">
-        <v>0.02315152844814977</v>
+        <v>0.03412088858404012</v>
       </c>
       <c r="X2">
-        <v>0.06591110772994889</v>
+        <v>0.05672345665120607</v>
       </c>
       <c r="Y2">
-        <v>-0.04275957928179912</v>
+        <v>-0.02260256806716596</v>
       </c>
       <c r="Z2">
-        <v>2.313012094292559</v>
+        <v>1.088325224456237</v>
       </c>
       <c r="AA2">
-        <v>2.321411876257187e-05</v>
+        <v>2.989405553352569e-05</v>
       </c>
       <c r="AB2">
-        <v>0.06570689281610761</v>
+        <v>0.05649368785641091</v>
       </c>
       <c r="AC2">
-        <v>-0.06555270361180884</v>
+        <v>-0.05647296924656112</v>
       </c>
       <c r="AD2">
-        <v>693.5690000000001</v>
+        <v>175.81</v>
       </c>
       <c r="AE2">
-        <v>13.11993365056498</v>
+        <v>11.84249089518141</v>
       </c>
       <c r="AF2">
-        <v>706.688933650565</v>
+        <v>187.6524908951814</v>
       </c>
       <c r="AG2">
-        <v>-19.475066349435</v>
+        <v>110.1634908951814</v>
       </c>
       <c r="AH2">
-        <v>0.1234018480424354</v>
+        <v>0.036159667182172</v>
       </c>
       <c r="AI2">
-        <v>0.4145924271363332</v>
+        <v>0.1848515297733307</v>
       </c>
       <c r="AJ2">
-        <v>-0.003894573234792015</v>
+        <v>0.0215497110103166</v>
       </c>
       <c r="AK2">
-        <v>-0.01990552464050626</v>
+        <v>0.1174872349887581</v>
       </c>
       <c r="AL2">
-        <v>0.227</v>
+        <v>0.053</v>
       </c>
       <c r="AM2">
-        <v>0.141</v>
+        <v>-0.159</v>
       </c>
       <c r="AN2">
-        <v>69.74748592115849</v>
+        <v>52.82752403846154</v>
       </c>
       <c r="AO2">
-        <v>15.37444933920705</v>
+        <v>-50.56603773584906</v>
       </c>
       <c r="AP2">
-        <v>-1.958474089846641</v>
+        <v>33.10201048533096</v>
       </c>
       <c r="AQ2">
-        <v>24.7517730496454</v>
+        <v>16.85534591194968</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mwb fairtrade Wertpapierhandelsbank AG (XTRA:MWB)</t>
+          <t>Baader Bank Aktiengesellschaft (XTRA:BWB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,10 +725,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.257</v>
-      </c>
-      <c r="E3">
-        <v>0.059</v>
+        <v>0.138</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,34 +734,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.05690968498531018</v>
+        <v>0.0003558251823150007</v>
       </c>
       <c r="J3">
-        <v>0.03649880758192489</v>
+        <v>0.000267271403910815</v>
       </c>
       <c r="K3">
-        <v>6.63</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>0.1078048780487805</v>
+        <v>0.0117603822124219</v>
       </c>
       <c r="M3">
-        <v>10.8916</v>
+        <v>2.684</v>
       </c>
       <c r="N3">
-        <v>0.1861811965811966</v>
+        <v>0.01476347634763476</v>
       </c>
       <c r="O3">
-        <v>1.642775263951735</v>
+        <v>0.8387499999999999</v>
       </c>
       <c r="P3">
-        <v>10.8916</v>
+        <v>2.684</v>
       </c>
       <c r="Q3">
-        <v>0.1861811965811966</v>
+        <v>0.01476347634763476</v>
       </c>
       <c r="R3">
-        <v>1.642775263951735</v>
+        <v>0.8387499999999999</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,55 +770,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.001</v>
+        <v>19.2</v>
       </c>
       <c r="V3">
-        <v>1.70940170940171e-05</v>
+        <v>0.1056105610561056</v>
       </c>
       <c r="W3">
-        <v>0.1453947368421052</v>
+        <v>0.0179472798653954</v>
       </c>
       <c r="X3">
-        <v>0.07338139156130093</v>
+        <v>0.06508419036315564</v>
       </c>
       <c r="Y3">
-        <v>0.07201334528080432</v>
-      </c>
-      <c r="Z3">
-        <v>0.9731124771406749</v>
-      </c>
-      <c r="AA3">
-        <v>0.03551744505872777</v>
+        <v>-0.04713691049776024</v>
       </c>
       <c r="AB3">
-        <v>0.06338481269483298</v>
-      </c>
-      <c r="AC3">
-        <v>-0.02786736763610521</v>
+        <v>0.0515036295342381</v>
       </c>
       <c r="AD3">
-        <v>16.4</v>
+        <v>119.2</v>
       </c>
       <c r="AE3">
-        <v>7.100271867017121</v>
+        <v>4.410899839460441</v>
       </c>
       <c r="AF3">
-        <v>23.50027186701712</v>
+        <v>123.6108998394604</v>
       </c>
       <c r="AG3">
-        <v>23.49927186701712</v>
+        <v>104.4108998394604</v>
       </c>
       <c r="AH3">
-        <v>0.2865877311373843</v>
+        <v>0.404736372881376</v>
       </c>
       <c r="AI3">
-        <v>0.4174095628263652</v>
+        <v>0.4070018557279318</v>
       </c>
       <c r="AJ3">
-        <v>0.2865790309105088</v>
+        <v>0.3648040654567171</v>
       </c>
       <c r="AK3">
-        <v>0.4173992147273959</v>
+        <v>0.3669838304907681</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -830,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>3.333333333333333</v>
+        <v>121.7568947906027</v>
       </c>
       <c r="AP3">
-        <v>4.776274769718927</v>
+        <v>106.6505616337696</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bitcoin Group SE (XTRA:ADE)</t>
+          <t>mwb fairtrade Wertpapierhandelsbank AG (XTRA:MWB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,46 +841,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.444</v>
-      </c>
-      <c r="E4">
-        <v>0.0788</v>
+        <v>0.127</v>
       </c>
       <c r="G4">
-        <v>1.611510791366906</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1.611510791366906</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.2510791366906475</v>
+        <v>0.08295694687927595</v>
       </c>
       <c r="J4">
-        <v>0.1255395683453237</v>
+        <v>0.08295694687927595</v>
       </c>
       <c r="K4">
-        <v>1.03</v>
+        <v>-0.378</v>
       </c>
       <c r="L4">
-        <v>0.07410071942446043</v>
+        <v>-0.009569620253164556</v>
       </c>
       <c r="M4">
-        <v>0.523</v>
+        <v>1.30375</v>
       </c>
       <c r="N4">
-        <v>0.005522703273495248</v>
+        <v>0.05768805309734513</v>
       </c>
       <c r="O4">
-        <v>0.5077669902912622</v>
+        <v>-3.449074074074074</v>
       </c>
       <c r="P4">
-        <v>0.523</v>
+        <v>1.30375</v>
       </c>
       <c r="Q4">
-        <v>0.005522703273495248</v>
+        <v>0.05768805309734513</v>
       </c>
       <c r="R4">
-        <v>0.5077669902912622</v>
+        <v>-3.449074074074074</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,73 +886,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>20.2</v>
+        <v>2.17</v>
       </c>
       <c r="V4">
-        <v>0.2133051742344245</v>
+        <v>0.09601769911504424</v>
       </c>
       <c r="W4">
-        <v>0.007540263543191802</v>
+        <v>-0.01152439024390244</v>
       </c>
       <c r="X4">
-        <v>0.06588897361143775</v>
+        <v>0.06888992572498094</v>
       </c>
       <c r="Y4">
-        <v>-0.05834871006824595</v>
+        <v>-0.08041431596888338</v>
       </c>
       <c r="Z4">
-        <v>0.1244270982526497</v>
+        <v>0.700789459836749</v>
       </c>
       <c r="AA4">
-        <v>0.01562052420509883</v>
+        <v>0.05813535399323367</v>
       </c>
       <c r="AB4">
-        <v>0.06574827239495272</v>
+        <v>0.05236812892214276</v>
       </c>
       <c r="AC4">
-        <v>-0.05012774818985389</v>
+        <v>0.005767225071090912</v>
       </c>
       <c r="AD4">
-        <v>0.489</v>
+        <v>15.1</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>7.166002991343</v>
       </c>
       <c r="AF4">
-        <v>0.489</v>
+        <v>22.266002991343</v>
       </c>
       <c r="AG4">
-        <v>-19.711</v>
+        <v>20.096002991343</v>
       </c>
       <c r="AH4">
-        <v>0.005137148199897046</v>
+        <v>0.496277838603971</v>
       </c>
       <c r="AI4">
-        <v>0.005780893496790363</v>
+        <v>0.4996185768705396</v>
       </c>
       <c r="AJ4">
-        <v>-0.2628518849431249</v>
+        <v>0.4706764470533142</v>
       </c>
       <c r="AK4">
-        <v>-0.3061237167839227</v>
+        <v>0.4740070189033263</v>
       </c>
       <c r="AL4">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.008000000000000007</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.1373595505617977</v>
-      </c>
-      <c r="AO4">
-        <v>47.16216216216217</v>
+        <v>3.205944798301486</v>
       </c>
       <c r="AP4">
-        <v>-5.536797752808988</v>
-      </c>
-      <c r="AQ4">
-        <v>-436.2499999999997</v>
+        <v>4.266667301771338</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lang &amp; Schwarz Aktiengesellschaft (XTRA:LUS1)</t>
+          <t>JDC Group AG (XTRA:JDC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,112 +966,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.322</v>
+        <v>0.124</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.009612044006948466</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.00122834882320175</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.001126189119093882</v>
       </c>
       <c r="K5">
-        <v>-18.7</v>
+        <v>1.76</v>
       </c>
       <c r="L5">
-        <v>-0.0210727969348659</v>
+        <v>0.01019108280254777</v>
       </c>
       <c r="M5">
-        <v>14.8208</v>
+        <v>1.883</v>
       </c>
       <c r="N5">
-        <v>0.1688018223234624</v>
+        <v>0.00641130405175349</v>
       </c>
       <c r="O5">
-        <v>-0.7925561497326203</v>
+        <v>1.069886363636364</v>
       </c>
       <c r="P5">
-        <v>14.8208</v>
+        <v>0.033</v>
       </c>
       <c r="Q5">
-        <v>0.1688018223234624</v>
+        <v>0.0001123595505617978</v>
       </c>
       <c r="R5">
-        <v>-0.7925561497326203</v>
+        <v>0.01875</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.9824747742963357</v>
       </c>
       <c r="U5">
-        <v>684.4</v>
+        <v>36</v>
       </c>
       <c r="V5">
-        <v>7.79498861047836</v>
+        <v>0.1225740551583248</v>
       </c>
       <c r="W5">
-        <v>-0.1833333333333333</v>
+        <v>0.04718498659517427</v>
       </c>
       <c r="X5">
-        <v>0.1879567517278754</v>
+        <v>0.05797711856005283</v>
       </c>
       <c r="Y5">
-        <v>-0.3712900850612088</v>
+        <v>-0.01079213196487856</v>
       </c>
       <c r="Z5">
-        <v>26.89090909090909</v>
+        <v>4.37776865447773</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.004930195424583081</v>
       </c>
       <c r="AB5">
-        <v>0.05851876857621274</v>
+        <v>0.05576298524922241</v>
       </c>
       <c r="AC5">
-        <v>-0.05851876857621274</v>
+        <v>-0.05083278982463933</v>
       </c>
       <c r="AD5">
-        <v>567.7</v>
+        <v>32</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.2493207911652892</v>
       </c>
       <c r="AF5">
-        <v>567.7</v>
+        <v>32.24932079116529</v>
       </c>
       <c r="AG5">
-        <v>-116.6999999999999</v>
+        <v>-3.750679208834711</v>
       </c>
       <c r="AH5">
-        <v>0.8660564454614799</v>
+        <v>0.09893967783975635</v>
       </c>
       <c r="AI5">
-        <v>0.907158836689038</v>
+        <v>0.3717530062143106</v>
       </c>
       <c r="AJ5">
-        <v>4.038062283737031</v>
+        <v>-0.01293563716100622</v>
       </c>
       <c r="AK5">
-        <v>1.99146757679181</v>
+        <v>-0.07390599815648467</v>
       </c>
       <c r="AL5">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.153</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
+        <v>-0.132</v>
+      </c>
+      <c r="AN5">
+        <v>122.1374045801527</v>
+      </c>
+      <c r="AP5">
+        <v>-14.31556949936913</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JDC Group AG (XTRA:JDC)</t>
+          <t>EUWAX Aktiengesellschaft (DB:EUX)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,112 +1094,109 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.141</v>
+        <v>0.128</v>
+      </c>
+      <c r="E6">
+        <v>0.048</v>
       </c>
       <c r="G6">
-        <v>0.01023672424824056</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.001249602023087209</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.0009724793975590254</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1.15</v>
+        <v>6.09</v>
       </c>
       <c r="L6">
-        <v>0.007357645553422903</v>
+        <v>0.1545685279187817</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>4.67</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.01702515493984688</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.7668308702791461</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>4.67</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.01702515493984688</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.7668308702791461</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>17.4</v>
+        <v>3.82</v>
       </c>
       <c r="V6">
-        <v>0.0748709122203098</v>
+        <v>0.01392635800218739</v>
       </c>
       <c r="W6">
-        <v>0.03616352201257862</v>
+        <v>0.0678173719376392</v>
       </c>
       <c r="X6">
-        <v>0.06737906194646059</v>
+        <v>0.05681010570836842</v>
       </c>
       <c r="Y6">
-        <v>-0.03121553993388198</v>
+        <v>0.01100726622927078</v>
       </c>
       <c r="Z6">
-        <v>3.187945867568874</v>
+        <v>0.4539170506912442</v>
       </c>
       <c r="AA6">
-        <v>0.003100211676744163</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06514047815488526</v>
+        <v>0.05640742498315798</v>
       </c>
       <c r="AC6">
-        <v>-0.06204026647814109</v>
+        <v>-0.05640742498315798</v>
       </c>
       <c r="AD6">
-        <v>19.3</v>
+        <v>4.44</v>
       </c>
       <c r="AE6">
-        <v>0.228436018957346</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>19.52843601895735</v>
+        <v>4.44</v>
       </c>
       <c r="AG6">
-        <v>2.128436018957348</v>
+        <v>0.6200000000000006</v>
       </c>
       <c r="AH6">
-        <v>0.07751580697896228</v>
+        <v>0.01592882255865681</v>
       </c>
       <c r="AI6">
-        <v>0.3436384561497148</v>
+        <v>0.04460518384569018</v>
       </c>
       <c r="AJ6">
-        <v>0.009075385719049023</v>
+        <v>0.002255201513167469</v>
       </c>
       <c r="AK6">
-        <v>0.05398225833593776</v>
+        <v>0.006477225240284168</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.004</v>
-      </c>
-      <c r="AN6">
-        <v>80.08298755186722</v>
-      </c>
-      <c r="AP6">
-        <v>8.8316847259641</v>
-      </c>
-      <c r="AQ6">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EUWAX Aktiengesellschaft (DB:EUX)</t>
+          <t>Tradegate AG Wertpapierhandelsbank (DB:T2G)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,10 +1216,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.198</v>
+        <v>0.117</v>
       </c>
       <c r="E7">
-        <v>-0.294</v>
+        <v>0.0857</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1249,34 +1228,34 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.001204230577755963</v>
+        <v>0.0001109487115210957</v>
       </c>
       <c r="J7">
-        <v>0.0006021152888779814</v>
+        <v>7.123821824348012e-05</v>
       </c>
       <c r="K7">
-        <v>1.09</v>
+        <v>29.5</v>
       </c>
       <c r="L7">
-        <v>0.02037383177570094</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="M7">
-        <v>6.16</v>
+        <v>45.384</v>
       </c>
       <c r="N7">
-        <v>0.02035018169805088</v>
+        <v>0.01545145036088792</v>
       </c>
       <c r="O7">
-        <v>5.651376146788991</v>
+        <v>1.538440677966102</v>
       </c>
       <c r="P7">
-        <v>6.16</v>
+        <v>45.384</v>
       </c>
       <c r="Q7">
-        <v>0.02035018169805088</v>
+        <v>0.01545145036088792</v>
       </c>
       <c r="R7">
-        <v>5.651376146788991</v>
+        <v>1.538440677966102</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1285,55 +1264,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3.66</v>
+        <v>0.246</v>
       </c>
       <c r="V7">
-        <v>0.01209117938553023</v>
+        <v>8.375323437287213e-05</v>
       </c>
       <c r="W7">
-        <v>0.01013953488372093</v>
+        <v>0.2116212338593974</v>
       </c>
       <c r="X7">
-        <v>0.06588272080438333</v>
+        <v>0.05661824102558174</v>
       </c>
       <c r="Y7">
-        <v>-0.0557431859206624</v>
+        <v>0.1550029928338157</v>
       </c>
       <c r="Z7">
-        <v>0.5121584093508398</v>
+        <v>0.8392701634213502</v>
       </c>
       <c r="AA7">
-        <v>0.0003083784085975683</v>
+        <v>5.978811106705137e-05</v>
       </c>
       <c r="AB7">
-        <v>0.06572510072634939</v>
+        <v>0.05659830162103131</v>
       </c>
       <c r="AC7">
-        <v>-0.06541672231775182</v>
+        <v>-0.05653851350996426</v>
       </c>
       <c r="AD7">
-        <v>0.66</v>
+        <v>2.32</v>
       </c>
       <c r="AE7">
-        <v>0.80286832045028</v>
+        <v>0.0162672732126812</v>
       </c>
       <c r="AF7">
-        <v>1.46286832045028</v>
+        <v>2.336267273212681</v>
       </c>
       <c r="AG7">
-        <v>-2.19713167954972</v>
+        <v>2.090267273212681</v>
       </c>
       <c r="AH7">
-        <v>0.004809490154166607</v>
+        <v>0.0007947740938674865</v>
       </c>
       <c r="AI7">
-        <v>0.0160291731716532</v>
+        <v>0.01773442744029942</v>
       </c>
       <c r="AJ7">
-        <v>-0.007311516498427372</v>
+        <v>0.0007111469379143108</v>
       </c>
       <c r="AK7">
-        <v>-0.02508059064359214</v>
+        <v>0.01589674518547817</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1342,10 +1321,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>2.933333333333334</v>
+        <v>136.4705882352941</v>
       </c>
       <c r="AP7">
-        <v>-9.765029686887646</v>
+        <v>122.9568984242754</v>
       </c>
     </row>
     <row r="8">
@@ -1365,10 +1344,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.251</v>
+        <v>0.103</v>
       </c>
       <c r="E8">
-        <v>0.252</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1383,28 +1362,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>36.6</v>
+        <v>7.33</v>
       </c>
       <c r="L8">
-        <v>0.1868300153139357</v>
+        <v>0.05873397435897436</v>
       </c>
       <c r="M8">
-        <v>14.07</v>
+        <v>14.497</v>
       </c>
       <c r="N8">
-        <v>0.01248447204968944</v>
+        <v>0.01408980464573817</v>
       </c>
       <c r="O8">
-        <v>0.3844262295081967</v>
+        <v>1.977762619372442</v>
       </c>
       <c r="P8">
-        <v>14.07</v>
+        <v>14.497</v>
       </c>
       <c r="Q8">
-        <v>0.01248447204968944</v>
+        <v>0.01408980464573817</v>
       </c>
       <c r="R8">
-        <v>0.3844262295081967</v>
+        <v>1.977762619372442</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1413,55 +1392,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.249</v>
+        <v>0.248</v>
       </c>
       <c r="V8">
-        <v>0.0002209405501330967</v>
+        <v>0.0002410341141024395</v>
       </c>
       <c r="W8">
-        <v>0.2304785894206549</v>
+        <v>0.04636306135357369</v>
       </c>
       <c r="X8">
-        <v>0.06593324184846003</v>
+        <v>0.05663643401637082</v>
       </c>
       <c r="Y8">
-        <v>0.1645453475721949</v>
+        <v>-0.01027337266279713</v>
       </c>
       <c r="Z8">
-        <v>1.127397662333178</v>
+        <v>0.7504013564947598</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06568868490586585</v>
+        <v>0.05657995072966383</v>
       </c>
       <c r="AC8">
-        <v>-0.06568868490586585</v>
+        <v>-0.05657995072966383</v>
       </c>
       <c r="AD8">
-        <v>8.460000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>8.460000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="AG8">
-        <v>8.211</v>
+        <v>2.072</v>
       </c>
       <c r="AH8">
-        <v>0.007450724816373981</v>
+        <v>0.002249762417330928</v>
       </c>
       <c r="AI8">
-        <v>0.0369496855345912</v>
+        <v>0.01107821602521249</v>
       </c>
       <c r="AJ8">
-        <v>0.007233016593391008</v>
+        <v>0.002009753902142832</v>
       </c>
       <c r="AK8">
-        <v>0.03590120282802314</v>
+        <v>0.009905723519400302</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1478,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tradegate AG Wertpapierhandelsbank (DB:T2G)</t>
+          <t>Sino AG (DB:XTP)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1487,10 +1466,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.27</v>
-      </c>
-      <c r="E9">
-        <v>0.356</v>
+        <v>-0.09849999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.008</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1499,34 +1478,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>8.053401812449186e-05</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>5.152320467906971e-05</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>66.59999999999999</v>
+        <v>-0.981</v>
       </c>
       <c r="L9">
-        <v>0.348326359832636</v>
+        <v>-0.1676923076923077</v>
       </c>
       <c r="M9">
-        <v>101.992</v>
+        <v>7.1136</v>
       </c>
       <c r="N9">
-        <v>0.03591773489223834</v>
+        <v>0.09459574468085107</v>
       </c>
       <c r="O9">
-        <v>1.531411411411411</v>
+        <v>-7.251376146788991</v>
       </c>
       <c r="P9">
-        <v>101.992</v>
+        <v>7.1136</v>
       </c>
       <c r="Q9">
-        <v>0.03591773489223834</v>
+        <v>0.09459574468085107</v>
       </c>
       <c r="R9">
-        <v>1.531411411411411</v>
+        <v>-7.251376146788991</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1535,67 +1514,61 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.248</v>
+        <v>0.005</v>
       </c>
       <c r="V9">
-        <v>8.733624454148472e-05</v>
+        <v>6.648936170212766e-05</v>
       </c>
       <c r="W9">
-        <v>0.3377281947261663</v>
+        <v>-0.005888355342136855</v>
       </c>
       <c r="X9">
-        <v>0.06584782175686035</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="Y9">
-        <v>0.271880372969306</v>
+        <v>-0.06249668097011246</v>
       </c>
       <c r="Z9">
-        <v>0.9011131550208928</v>
+        <v>0.03511488871281423</v>
       </c>
       <c r="AA9">
-        <v>4.642823752514374e-05</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06576641419312645</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="AC9">
-        <v>-0.06571998595560131</v>
+        <v>-0.0566083256279756</v>
       </c>
       <c r="AD9">
-        <v>8.460000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>0.01800947867298578</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>8.478009478672986</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>8.230009478672986</v>
+        <v>-0.005</v>
       </c>
       <c r="AH9">
-        <v>0.002976747634881267</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.05733110358031758</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0.002889923012005756</v>
+        <v>-6.649378283130527e-05</v>
       </c>
       <c r="AK9">
-        <v>0.05574753742640594</v>
+        <v>-0.0002538715410002539</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>445.2631578947369</v>
-      </c>
-      <c r="AP9">
-        <v>433.1583936143677</v>
       </c>
     </row>
     <row r="10">
@@ -1606,7 +1579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sino AG (DB:XTP)</t>
+          <t>Bitcoin Group SE (XTRA:ADE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1615,49 +1588,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.138</v>
+        <v>-0.153</v>
       </c>
       <c r="E10">
-        <v>1.914</v>
-      </c>
-      <c r="F10">
-        <v>-0.792</v>
+        <v>-0.299</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-0.4359255202628696</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>-0.4359255202628696</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>-0.2935377875136911</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>-0.2935377875136911</v>
       </c>
       <c r="K10">
-        <v>136.9</v>
+        <v>1.84</v>
       </c>
       <c r="L10">
-        <v>13.03809523809524</v>
+        <v>0.2015334063526835</v>
       </c>
       <c r="M10">
-        <v>145.548</v>
+        <v>0.545</v>
       </c>
       <c r="N10">
-        <v>2.267102803738318</v>
+        <v>0.002895855472901169</v>
       </c>
       <c r="O10">
-        <v>1.063170197224251</v>
+        <v>0.296195652173913</v>
       </c>
       <c r="P10">
-        <v>145.548</v>
+        <v>0.545</v>
       </c>
       <c r="Q10">
-        <v>2.267102803738318</v>
+        <v>0.002895855472901169</v>
       </c>
       <c r="R10">
-        <v>1.063170197224251</v>
+        <v>0.296195652173913</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1666,290 +1636,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.004</v>
+        <v>15.8</v>
       </c>
       <c r="V10">
-        <v>6.230529595015576e-05</v>
+        <v>0.08395324123273115</v>
       </c>
       <c r="W10">
-        <v>3.474619289340102</v>
+        <v>0.02187871581450654</v>
       </c>
       <c r="X10">
-        <v>0.06579141120325535</v>
+        <v>0.05663680759404373</v>
       </c>
       <c r="Y10">
-        <v>3.408827878136846</v>
+        <v>-0.03475809177953719</v>
       </c>
       <c r="Z10">
-        <v>0.2665583508923358</v>
+        <v>0.151336836347362</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>-0.04442308011072619</v>
       </c>
       <c r="AB10">
-        <v>0.06579141120325535</v>
+        <v>0.05658884877378482</v>
       </c>
       <c r="AC10">
-        <v>-0.06579141120325535</v>
+        <v>-0.101011928884511</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AG10">
-        <v>-0.004</v>
+        <v>-15.37</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.002279594974288289</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.003591414014866783</v>
       </c>
       <c r="AJ10">
-        <v>-6.230917814194032e-05</v>
+        <v>-0.08893131979401725</v>
       </c>
       <c r="AK10">
-        <v>-2.401018031645418e-05</v>
+        <v>-0.1478880015394978</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Valora Effekten Handel AG (DB:VEH)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>-0.118</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>-0.235</v>
-      </c>
-      <c r="L11">
-        <v>-0.5662650602409639</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
-      <c r="N11">
-        <v>-0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0.002</v>
-      </c>
-      <c r="V11">
-        <v>0.0007874015748031496</v>
-      </c>
-      <c r="W11">
-        <v>-0.09073359073359073</v>
-      </c>
-      <c r="X11">
-        <v>0.06579141120325535</v>
-      </c>
-      <c r="Y11">
-        <v>-0.1565250019368461</v>
-      </c>
-      <c r="Z11">
-        <v>0.160355486862442</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.06579141120325535</v>
-      </c>
-      <c r="AC11">
-        <v>-0.06579141120325535</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>-0.002</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.0007880220646178092</v>
-      </c>
-      <c r="AK11">
-        <v>-0.0009765625</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Baader Bank Aktiengesellschaft (XTRA:BWB)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.142</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>-5.90732775125433e-05</v>
-      </c>
-      <c r="J12">
-        <v>-2.953663875627165e-05</v>
-      </c>
-      <c r="K12">
-        <v>-1.22</v>
-      </c>
-      <c r="L12">
-        <v>-0.004782438259506076</v>
-      </c>
-      <c r="M12">
-        <v>-0</v>
-      </c>
-      <c r="N12">
-        <v>-0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>-0</v>
-      </c>
-      <c r="Q12">
-        <v>-0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>-0.006545064377682403</v>
-      </c>
-      <c r="X12">
-        <v>0.07270578070686279</v>
-      </c>
-      <c r="Y12">
-        <v>-0.07925084508454519</v>
-      </c>
-      <c r="AB12">
-        <v>0.06354164043257618</v>
-      </c>
-      <c r="AD12">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="AE12">
-        <v>4.970347965467249</v>
-      </c>
-      <c r="AF12">
-        <v>77.07034796546725</v>
-      </c>
-      <c r="AG12">
-        <v>77.07034796546725</v>
-      </c>
-      <c r="AH12">
-        <v>0.2679120337238198</v>
-      </c>
-      <c r="AI12">
-        <v>0.3155124991935688</v>
-      </c>
-      <c r="AJ12">
-        <v>0.2679120337238198</v>
-      </c>
-      <c r="AK12">
-        <v>0.3155124991935688</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>73.64657814096016</v>
-      </c>
-      <c r="AP12">
-        <v>78.72354235492058</v>
+        <v>-0.027</v>
+      </c>
+      <c r="AN10">
+        <v>-0.1628787878787879</v>
+      </c>
+      <c r="AO10">
+        <v>-50.56603773584906</v>
+      </c>
+      <c r="AP10">
+        <v>5.821969696969697</v>
+      </c>
+      <c r="AQ10">
+        <v>99.25925925925925</v>
       </c>
     </row>
   </sheetData>
